--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/8349-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/8349-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{213609ED-3E17-4106-B757-C80F78CE3296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9B9CD06-CAAB-4D22-8704-1B7C57C63CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{C0A5E0E9-D712-4F1B-95D2-D3742CE2E229}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{4CB002F3-5034-408A-A520-740DC9792EB3}"/>
   </bookViews>
   <sheets>
     <sheet name="8349-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1556,27 +1556,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B774D5E-5168-42F0-AED3-1FEBF1C1E165}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FDA2724-E981-4C29-9F60-81C5163981A8}">
   <dimension ref="A1:X34"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1610,7 +1609,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1646,7 +1645,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1698,7 +1697,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1766,7 +1765,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1838,7 +1837,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39"/>
       <c r="B6" s="40"/>
       <c r="C6" s="13" t="s">
@@ -1866,7 +1865,7 @@
       <c r="W6" s="46"/>
       <c r="X6" s="42"/>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="47">
         <v>2023</v>
       </c>
@@ -1938,7 +1937,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="49"/>
       <c r="B8" s="50"/>
       <c r="C8" s="16" t="s">
@@ -1966,7 +1965,7 @@
       <c r="W8" s="56"/>
       <c r="X8" s="52"/>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2022</v>
       </c>
@@ -2038,7 +2037,7 @@
         <v>5.49</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39"/>
       <c r="B10" s="40"/>
       <c r="C10" s="13" t="s">
@@ -2066,7 +2065,7 @@
       <c r="W10" s="46"/>
       <c r="X10" s="42"/>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="47">
         <v>2021</v>
       </c>
@@ -2138,7 +2137,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="49"/>
       <c r="B12" s="50"/>
       <c r="C12" s="16" t="s">
@@ -2166,7 +2165,7 @@
       <c r="W12" s="56"/>
       <c r="X12" s="52"/>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="57">
         <v>2020</v>
       </c>
@@ -2238,7 +2237,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="59">
         <v>2019</v>
       </c>
@@ -2310,7 +2309,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="57">
         <v>2018</v>
       </c>
@@ -2382,7 +2381,7 @@
         <v>7.89</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="59">
         <v>2017</v>
       </c>
@@ -2454,7 +2453,7 @@
         <v>8.7200000000000006</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="57">
         <v>2016</v>
       </c>
@@ -2526,7 +2525,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="59">
         <v>2015</v>
       </c>
@@ -2598,7 +2597,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="57">
         <v>2014</v>
       </c>
@@ -2670,7 +2669,7 @@
         <v>5.46</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="59">
         <v>2013</v>
       </c>
@@ -2742,7 +2741,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="57">
         <v>2012</v>
       </c>
@@ -2814,7 +2813,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="59">
         <v>2011</v>
       </c>
@@ -2886,7 +2885,7 @@
         <v>7.66</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="57">
         <v>2010</v>
       </c>
@@ -2958,7 +2957,7 @@
         <v>5.46</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="59">
         <v>2009</v>
       </c>
@@ -3030,7 +3029,7 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="57">
         <v>2008</v>
       </c>
@@ -3102,7 +3101,7 @@
         <v>3.18</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="59">
         <v>2007</v>
       </c>
@@ -3174,7 +3173,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="57">
         <v>2006</v>
       </c>
@@ -3246,7 +3245,7 @@
         <v>8.1300000000000008</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="59">
         <v>2005</v>
       </c>
@@ -3318,7 +3317,7 @@
         <v>9.34</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="57">
         <v>2004</v>
       </c>
@@ -3390,7 +3389,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="59">
         <v>2003</v>
       </c>
@@ -3462,7 +3461,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="57">
         <v>2002</v>
       </c>
@@ -3534,7 +3533,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="59">
         <v>2000</v>
       </c>
@@ -3606,7 +3605,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="57">
         <v>1999</v>
       </c>
@@ -3678,7 +3677,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="59" t="s">
         <v>54</v>
       </c>
